--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-04-05T22:15:32.233Z</t>
+    <t>2026-04-05T22:51:50.575Z</t>
   </si>
   <si>
     <t>SHRM Home - The Voice of All Things Work</t>

--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-04-05T22:51:50.575Z</t>
+    <t>2026-04-05T23:03:28.314Z</t>
   </si>
   <si>
     <t>SHRM Home - The Voice of All Things Work</t>
